--- a/Historical Excel/Round 3/Trades day 1 (Round 3).xlsx
+++ b/Historical Excel/Round 3/Trades day 1 (Round 3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Historical Excel/Round 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{968B9C4A-9656-4D72-9110-F6116D3E7370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F9BF6CC-B19C-46CD-BDD0-A2A44BDF4A8C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{968B9C4A-9656-4D72-9110-F6116D3E7370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BA68E2B-8175-40C5-B4EF-1C6BD9E2557D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{318DEC54-EEA3-4132-AAC3-FEBC3D7EB1B7}"/>
   </bookViews>
@@ -216,7 +216,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-AU"/>
-              <a:t>Hydrogen Pack</a:t>
+              <a:t>Hydrogen Pack Day 1</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -7302,7 +7302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA335C4-D622-4454-9704-6849DCB26349}">
-  <dimension ref="A1:G1408"/>
+  <dimension ref="A1:K1408"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
@@ -15778,7 +15778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>977600</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>979200</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>982900</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>985400</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>985800</v>
       </c>
@@ -15893,7 +15893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>988000</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>988400</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>989000</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>6100</v>
       </c>
@@ -15984,8 +15984,12 @@
       <c r="G377">
         <v>3</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="K377">
+        <f>AVERAGE(F377:F826)</f>
+        <v>5247.2111111111108</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>9400</v>
       </c>
@@ -16008,7 +16012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>10400</v>
       </c>
@@ -16031,7 +16035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>14300</v>
       </c>
@@ -16054,7 +16058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>14800</v>
       </c>
@@ -16077,7 +16081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>17400</v>
       </c>
@@ -16100,7 +16104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>19300</v>
       </c>
@@ -16123,7 +16127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>20200</v>
       </c>

--- a/Historical Excel/Round 3/Trades day 1 (Round 3).xlsx
+++ b/Historical Excel/Round 3/Trades day 1 (Round 3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Historical Excel/Round 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{968B9C4A-9656-4D72-9110-F6116D3E7370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BA68E2B-8175-40C5-B4EF-1C6BD9E2557D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{968B9C4A-9656-4D72-9110-F6116D3E7370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{517FD8DC-7BD6-4334-A7A3-67EBBC876A6E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{318DEC54-EEA3-4132-AAC3-FEBC3D7EB1B7}"/>
   </bookViews>
@@ -6875,16 +6875,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>304799</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>414866</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>33866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>491067</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>12699</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6911,16 +6911,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>451828</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>333295</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>85482</xdr:rowOff>
+      <xdr:rowOff>68549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>387048</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>268515</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>107254</xdr:rowOff>
+      <xdr:rowOff>90321</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7314,7 +7314,7 @@
     <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>5100</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>6200</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>15000</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>22800</v>
       </c>
@@ -7428,8 +7428,12 @@
       <c r="G5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <f>AVERAGE(F2:F376)</f>
+        <v>9993.6080000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>30800</v>
       </c>
@@ -7452,7 +7456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>31400</v>
       </c>
@@ -7475,7 +7479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>32000</v>
       </c>
@@ -7498,7 +7502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>33600</v>
       </c>
@@ -7521,7 +7525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>37400</v>
       </c>
@@ -7544,7 +7548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>40900</v>
       </c>
@@ -7567,7 +7571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>41300</v>
       </c>
@@ -7590,7 +7594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>43900</v>
       </c>
@@ -7613,7 +7617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>45200</v>
       </c>
@@ -7636,7 +7640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>48300</v>
       </c>
@@ -7659,7 +7663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>52400</v>
       </c>
